--- a/data/M3/M3selected.xlsx
+++ b/data/M3/M3selected.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10409"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Ongoing\segmentation\data\M3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lisavecchi/Desktop/segmentation/data/M3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FAF09D4-E552-4C87-8743-E5029697D6A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B36D55E-EBF8-5741-A12B-85D45FDD1E0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2088" yWindow="1224" windowWidth="19212" windowHeight="10884" activeTab="3" xr2:uid="{688A4006-9200-421D-B73F-75AE198D8BAB}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="3" xr2:uid="{688A4006-9200-421D-B73F-75AE198D8BAB}"/>
   </bookViews>
   <sheets>
     <sheet name="M3 series" sheetId="1" r:id="rId1"/>
@@ -138,7 +138,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -156,7 +156,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="it-IT"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -193,7 +193,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="it-IT"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -729,7 +729,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1238255456"/>
@@ -788,7 +788,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1238256416"/>
@@ -836,7 +836,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="it-IT"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -850,7 +850,7 @@
 <file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="it-IT"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -887,7 +887,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="it-IT"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -1304,7 +1304,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1351667936"/>
@@ -1363,7 +1363,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1351666976"/>
@@ -1404,7 +1404,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="it-IT"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -1418,7 +1418,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="it-IT"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1455,7 +1455,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="it-IT"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -1992,7 +1992,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1299140368"/>
@@ -2051,7 +2051,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1299139408"/>
@@ -2092,7 +2092,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="it-IT"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -2106,7 +2106,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="it-IT"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2143,7 +2143,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="it-IT"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -2680,7 +2680,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1299138928"/>
@@ -2739,7 +2739,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1299132208"/>
@@ -2780,7 +2780,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="it-IT"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -2794,7 +2794,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="it-IT"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2831,7 +2831,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="it-IT"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -3368,7 +3368,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1299138448"/>
@@ -3427,7 +3427,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1299135568"/>
@@ -3468,7 +3468,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="it-IT"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -3482,7 +3482,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="it-IT"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3519,7 +3519,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="it-IT"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -4056,7 +4056,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1299139888"/>
@@ -4115,7 +4115,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1299142768"/>
@@ -4156,7 +4156,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="it-IT"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -4170,7 +4170,7 @@
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="it-IT"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4207,7 +4207,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="it-IT"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -4624,7 +4624,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1351668896"/>
@@ -4683,7 +4683,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1351678496"/>
@@ -4724,7 +4724,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="it-IT"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -4738,7 +4738,7 @@
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="it-IT"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4775,7 +4775,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="it-IT"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -5192,7 +5192,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1351676576"/>
@@ -5251,7 +5251,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1351674176"/>
@@ -5292,7 +5292,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="it-IT"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -5306,7 +5306,7 @@
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="it-IT"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -5343,7 +5343,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="it-IT"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -5760,7 +5760,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1351676576"/>
@@ -5819,7 +5819,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1351672256"/>
@@ -5860,7 +5860,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="it-IT"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -5874,7 +5874,7 @@
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="it-IT"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -5911,7 +5911,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="it-IT"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -6328,7 +6328,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1351667936"/>
@@ -6387,7 +6387,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1351666976"/>
@@ -6428,7 +6428,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="it-IT"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -19122,9 +19122,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78542E84-EF4D-44A4-8837-BCCF362D5BC7}">
   <dimension ref="A1:ET11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:150" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -19456,7 +19456,7 @@
         <v>4249.63</v>
       </c>
     </row>
-    <row r="2" spans="1:150" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -19788,7 +19788,7 @@
         <v>6222.02</v>
       </c>
     </row>
-    <row r="3" spans="1:150" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -20120,7 +20120,7 @@
         <v>4646.5</v>
       </c>
     </row>
-    <row r="4" spans="1:150" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -20452,7 +20452,7 @@
         <v>5425</v>
       </c>
     </row>
-    <row r="5" spans="1:150" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -20784,7 +20784,7 @@
         <v>5294.78</v>
       </c>
     </row>
-    <row r="7" spans="1:150" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -21236,7 +21236,7 @@
         <v>11259.5</v>
       </c>
     </row>
-    <row r="8" spans="1:150" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -21688,7 +21688,7 @@
         <v>7190</v>
       </c>
     </row>
-    <row r="9" spans="1:150" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -22140,7 +22140,7 @@
         <v>7425</v>
       </c>
     </row>
-    <row r="10" spans="1:150" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -22592,7 +22592,7 @@
         <v>6505</v>
       </c>
     </row>
-    <row r="11" spans="1:150" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:150" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -23052,9 +23052,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86E7BF23-D5B3-4B32-ABE1-8AA2AD8385AD}">
   <dimension ref="A1:K150"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -23086,7 +23086,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>104</v>
       </c>
@@ -23118,7 +23118,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>8</v>
       </c>
@@ -23150,7 +23150,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -23182,7 +23182,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>0</v>
       </c>
@@ -23214,7 +23214,7 @@
         <v>1981</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>0</v>
       </c>
@@ -23246,7 +23246,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>3060.42</v>
       </c>
@@ -23278,7 +23278,7 @@
         <v>4815</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>3021.19</v>
       </c>
@@ -23310,7 +23310,7 @@
         <v>4820</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>3301.13</v>
       </c>
@@ -23342,7 +23342,7 @@
         <v>4835</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>3287.03</v>
       </c>
@@ -23374,7 +23374,7 @@
         <v>5020</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>3080.71</v>
       </c>
@@ -23406,7 +23406,7 @@
         <v>5020</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>3160.68</v>
       </c>
@@ -23438,7 +23438,7 @@
         <v>5030</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>3077.17</v>
       </c>
@@ -23470,7 +23470,7 @@
         <v>5060</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>3023.04</v>
       </c>
@@ -23502,7 +23502,7 @@
         <v>5060</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>2976.01</v>
       </c>
@@ -23534,7 +23534,7 @@
         <v>5090</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>3199.55</v>
       </c>
@@ -23566,7 +23566,7 @@
         <v>5095</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>3219.28</v>
       </c>
@@ -23598,7 +23598,7 @@
         <v>5095</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>3266.87</v>
       </c>
@@ -23630,7 +23630,7 @@
         <v>5065</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>3228.6</v>
       </c>
@@ -23662,7 +23662,7 @@
         <v>5055</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>3108.45</v>
       </c>
@@ -23694,7 +23694,7 @@
         <v>5045</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>3052.15</v>
       </c>
@@ -23726,7 +23726,7 @@
         <v>5045</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>3081.1</v>
       </c>
@@ -23758,7 +23758,7 @@
         <v>5100</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>3072.48</v>
       </c>
@@ -23790,7 +23790,7 @@
         <v>5100</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>2989.99</v>
       </c>
@@ -23822,7 +23822,7 @@
         <v>5095</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>2983.53</v>
       </c>
@@ -23854,7 +23854,7 @@
         <v>5160</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>2978.99</v>
       </c>
@@ -23886,7 +23886,7 @@
         <v>5210</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>3075.09</v>
       </c>
@@ -23918,7 +23918,7 @@
         <v>5250</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>3259.02</v>
       </c>
@@ -23950,7 +23950,7 @@
         <v>5250</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>3252.64</v>
       </c>
@@ -23982,7 +23982,7 @@
         <v>5255</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>3197.5</v>
       </c>
@@ -24014,7 +24014,7 @@
         <v>5135</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>3095.91</v>
       </c>
@@ -24046,7 +24046,7 @@
         <v>5220</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>3213.78</v>
       </c>
@@ -24078,7 +24078,7 @@
         <v>5245</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>3174.21</v>
       </c>
@@ -24110,7 +24110,7 @@
         <v>5245</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>3196.42</v>
       </c>
@@ -24142,7 +24142,7 @@
         <v>5365</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>3752.91</v>
       </c>
@@ -24174,7 +24174,7 @@
         <v>5365</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>4238.37</v>
       </c>
@@ -24206,7 +24206,7 @@
         <v>5365</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>4140.09</v>
       </c>
@@ -24238,7 +24238,7 @@
         <v>5210</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>3959.7</v>
       </c>
@@ -24270,7 +24270,7 @@
         <v>5210</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>3892.21</v>
       </c>
@@ -24302,7 +24302,7 @@
         <v>5190</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>3892.16</v>
       </c>
@@ -24334,7 +24334,7 @@
         <v>5180</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>3757.58</v>
       </c>
@@ -24366,7 +24366,7 @@
         <v>5180</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>3738.49</v>
       </c>
@@ -24398,7 +24398,7 @@
         <v>5245</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>3626.78</v>
       </c>
@@ -24430,7 +24430,7 @@
         <v>5245</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>3658.79</v>
       </c>
@@ -24462,7 +24462,7 @@
         <v>5305</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>3723.11</v>
       </c>
@@ -24494,7 +24494,7 @@
         <v>5195</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>3710.43</v>
       </c>
@@ -24526,7 +24526,7 @@
         <v>5235</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>3640.67</v>
       </c>
@@ -24558,7 +24558,7 @@
         <v>5350</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>3676.83</v>
       </c>
@@ -24590,7 +24590,7 @@
         <v>5310</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>3642.97</v>
       </c>
@@ -24622,7 +24622,7 @@
         <v>5245</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>3676.8</v>
       </c>
@@ -24654,7 +24654,7 @@
         <v>5345</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>3635.68</v>
       </c>
@@ -24686,7 +24686,7 @@
         <v>5375</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>3687.71</v>
       </c>
@@ -24718,7 +24718,7 @@
         <v>5375</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>3649.13</v>
       </c>
@@ -24750,7 +24750,7 @@
         <v>5375</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>3857.15</v>
       </c>
@@ -24782,7 +24782,7 @@
         <v>5375</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>3930.03</v>
       </c>
@@ -24814,7 +24814,7 @@
         <v>5375</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>3737.96</v>
       </c>
@@ -24846,7 +24846,7 @@
         <v>5390</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>3774.24</v>
       </c>
@@ -24878,7 +24878,7 @@
         <v>5365</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>3767.55</v>
       </c>
@@ -24910,7 +24910,7 @@
         <v>5365</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>3699.6</v>
       </c>
@@ -24942,7 +24942,7 @@
         <v>5325</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>3620.3</v>
       </c>
@@ -24974,7 +24974,7 @@
         <v>5160</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>3641</v>
       </c>
@@ -25006,7 +25006,7 @@
         <v>5315</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>3656.02</v>
       </c>
@@ -25038,7 +25038,7 @@
         <v>5310</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>3710.94</v>
       </c>
@@ -25070,7 +25070,7 @@
         <v>5335</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>3913.79</v>
       </c>
@@ -25102,7 +25102,7 @@
         <v>5335</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>3829.84</v>
       </c>
@@ -25134,7 +25134,7 @@
         <v>5340</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>3856.37</v>
       </c>
@@ -25166,7 +25166,7 @@
         <v>5340</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>3712.15</v>
       </c>
@@ -25198,7 +25198,7 @@
         <v>5335</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>3829.26</v>
       </c>
@@ -25230,7 +25230,7 @@
         <v>5115</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>4048.86</v>
       </c>
@@ -25262,7 +25262,7 @@
         <v>5335</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>4420.1400000000003</v>
       </c>
@@ -25294,7 +25294,7 @@
         <v>5255</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>4603.3</v>
       </c>
@@ -25326,7 +25326,7 @@
         <v>5350</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>4738.4399999999996</v>
       </c>
@@ -25358,7 +25358,7 @@
         <v>4750</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>4762.83</v>
       </c>
@@ -25390,7 +25390,7 @@
         <v>5225</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>4812.26</v>
       </c>
@@ -25422,7 +25422,7 @@
         <v>5295</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>4816.1000000000004</v>
       </c>
@@ -25454,7 +25454,7 @@
         <v>5295</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>4680.41</v>
       </c>
@@ -25486,7 +25486,7 @@
         <v>5290</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>4521.21</v>
       </c>
@@ -25518,7 +25518,7 @@
         <v>5330</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>4586.8</v>
       </c>
@@ -25550,7 +25550,7 @@
         <v>5360</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>4585.28</v>
       </c>
@@ -25582,7 +25582,7 @@
         <v>5370</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>4556.63</v>
       </c>
@@ -25614,7 +25614,7 @@
         <v>5370</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>4292.6899999999996</v>
       </c>
@@ -25646,7 +25646,7 @@
         <v>5360</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>4261.42</v>
       </c>
@@ -25678,7 +25678,7 @@
         <v>5360</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>4235.59</v>
       </c>
@@ -25710,7 +25710,7 @@
         <v>5365</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>4258.32</v>
       </c>
@@ -25742,7 +25742,7 @@
         <v>5360</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>4321.97</v>
       </c>
@@ -25774,7 +25774,7 @@
         <v>5360</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>4245.4399999999996</v>
       </c>
@@ -25806,7 +25806,7 @@
         <v>5365</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>4274.12</v>
       </c>
@@ -25838,7 +25838,7 @@
         <v>5385</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>4149.42</v>
       </c>
@@ -25870,7 +25870,7 @@
         <v>5295</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>4155.7</v>
       </c>
@@ -25902,7 +25902,7 @@
         <v>5420</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>4117.26</v>
       </c>
@@ -25934,7 +25934,7 @@
         <v>5470</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>4204.07</v>
       </c>
@@ -25966,7 +25966,7 @@
         <v>5475</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>4041.04</v>
       </c>
@@ -25998,7 +25998,7 @@
         <v>5500</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>4157.26</v>
       </c>
@@ -26030,7 +26030,7 @@
         <v>5500</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>4141.84</v>
       </c>
@@ -26062,7 +26062,7 @@
         <v>5490</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>4183.8999999999996</v>
       </c>
@@ -26094,7 +26094,7 @@
         <v>5495</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>4215.3900000000003</v>
       </c>
@@ -26126,7 +26126,7 @@
         <v>5515</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>4138.8900000000003</v>
       </c>
@@ -26158,7 +26158,7 @@
         <v>5465</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>4031.36</v>
       </c>
@@ -26190,7 +26190,7 @@
         <v>5455</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>4339.38</v>
       </c>
@@ -26222,7 +26222,7 @@
         <v>5500</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>4509.34</v>
       </c>
@@ -26254,7 +26254,7 @@
         <v>5460</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>4547.25</v>
       </c>
@@ -26286,7 +26286,7 @@
         <v>5545</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>4542.51</v>
       </c>
@@ -26318,7 +26318,7 @@
         <v>5625</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>4381.08</v>
       </c>
@@ -26350,7 +26350,7 @@
         <v>5715</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>4405.63</v>
       </c>
@@ -26382,7 +26382,7 @@
         <v>5715</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>4377.0200000000004</v>
       </c>
@@ -26414,7 +26414,7 @@
         <v>5715</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>4371.18</v>
       </c>
@@ -26446,7 +26446,7 @@
         <v>5710</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>4255.07</v>
       </c>
@@ -26478,7 +26478,7 @@
         <v>5715</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>4285.4399999999996</v>
       </c>
@@ -26510,7 +26510,7 @@
         <v>5715</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>4260.68</v>
       </c>
@@ -26542,7 +26542,7 @@
         <v>5670</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>4249.63</v>
       </c>
@@ -26574,7 +26574,7 @@
         <v>5660</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G111">
         <v>4042.5</v>
       </c>
@@ -26591,7 +26591,7 @@
         <v>5695</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G112">
         <v>6155</v>
       </c>
@@ -26608,7 +26608,7 @@
         <v>5695</v>
       </c>
     </row>
-    <row r="113" spans="7:11" x14ac:dyDescent="0.3">
+    <row r="113" spans="7:11" x14ac:dyDescent="0.2">
       <c r="G113">
         <v>6226</v>
       </c>
@@ -26625,7 +26625,7 @@
         <v>5545</v>
       </c>
     </row>
-    <row r="114" spans="7:11" x14ac:dyDescent="0.3">
+    <row r="114" spans="7:11" x14ac:dyDescent="0.2">
       <c r="G114">
         <v>3912</v>
       </c>
@@ -26642,7 +26642,7 @@
         <v>5535</v>
       </c>
     </row>
-    <row r="115" spans="7:11" x14ac:dyDescent="0.3">
+    <row r="115" spans="7:11" x14ac:dyDescent="0.2">
       <c r="G115">
         <v>6016</v>
       </c>
@@ -26659,7 +26659,7 @@
         <v>5535</v>
       </c>
     </row>
-    <row r="116" spans="7:11" x14ac:dyDescent="0.3">
+    <row r="116" spans="7:11" x14ac:dyDescent="0.2">
       <c r="G116">
         <v>5424.5</v>
       </c>
@@ -26676,7 +26676,7 @@
         <v>5535</v>
       </c>
     </row>
-    <row r="117" spans="7:11" x14ac:dyDescent="0.3">
+    <row r="117" spans="7:11" x14ac:dyDescent="0.2">
       <c r="G117">
         <v>6525</v>
       </c>
@@ -26693,7 +26693,7 @@
         <v>5670</v>
       </c>
     </row>
-    <row r="118" spans="7:11" x14ac:dyDescent="0.3">
+    <row r="118" spans="7:11" x14ac:dyDescent="0.2">
       <c r="G118">
         <v>6826</v>
       </c>
@@ -26710,7 +26710,7 @@
         <v>5680</v>
       </c>
     </row>
-    <row r="119" spans="7:11" x14ac:dyDescent="0.3">
+    <row r="119" spans="7:11" x14ac:dyDescent="0.2">
       <c r="G119">
         <v>7280</v>
       </c>
@@ -26727,7 +26727,7 @@
         <v>5780</v>
       </c>
     </row>
-    <row r="120" spans="7:11" x14ac:dyDescent="0.3">
+    <row r="120" spans="7:11" x14ac:dyDescent="0.2">
       <c r="G120">
         <v>6972.5</v>
       </c>
@@ -26744,7 +26744,7 @@
         <v>5845</v>
       </c>
     </row>
-    <row r="121" spans="7:11" x14ac:dyDescent="0.3">
+    <row r="121" spans="7:11" x14ac:dyDescent="0.2">
       <c r="G121">
         <v>5951</v>
       </c>
@@ -26761,7 +26761,7 @@
         <v>5840</v>
       </c>
     </row>
-    <row r="122" spans="7:11" x14ac:dyDescent="0.3">
+    <row r="122" spans="7:11" x14ac:dyDescent="0.2">
       <c r="G122">
         <v>8384.5</v>
       </c>
@@ -26778,7 +26778,7 @@
         <v>5840</v>
       </c>
     </row>
-    <row r="123" spans="7:11" x14ac:dyDescent="0.3">
+    <row r="123" spans="7:11" x14ac:dyDescent="0.2">
       <c r="G123">
         <v>5751</v>
       </c>
@@ -26795,7 +26795,7 @@
         <v>5840</v>
       </c>
     </row>
-    <row r="124" spans="7:11" x14ac:dyDescent="0.3">
+    <row r="124" spans="7:11" x14ac:dyDescent="0.2">
       <c r="G124">
         <v>6521.5</v>
       </c>
@@ -26812,7 +26812,7 @@
         <v>5845</v>
       </c>
     </row>
-    <row r="125" spans="7:11" x14ac:dyDescent="0.3">
+    <row r="125" spans="7:11" x14ac:dyDescent="0.2">
       <c r="G125">
         <v>7001.5</v>
       </c>
@@ -26829,7 +26829,7 @@
         <v>5845</v>
       </c>
     </row>
-    <row r="126" spans="7:11" x14ac:dyDescent="0.3">
+    <row r="126" spans="7:11" x14ac:dyDescent="0.2">
       <c r="G126">
         <v>7790.5</v>
       </c>
@@ -26846,7 +26846,7 @@
         <v>5845</v>
       </c>
     </row>
-    <row r="127" spans="7:11" x14ac:dyDescent="0.3">
+    <row r="127" spans="7:11" x14ac:dyDescent="0.2">
       <c r="G127">
         <v>6086</v>
       </c>
@@ -26863,7 +26863,7 @@
         <v>5855</v>
       </c>
     </row>
-    <row r="128" spans="7:11" x14ac:dyDescent="0.3">
+    <row r="128" spans="7:11" x14ac:dyDescent="0.2">
       <c r="G128">
         <v>7812.5</v>
       </c>
@@ -26880,7 +26880,7 @@
         <v>5995</v>
       </c>
     </row>
-    <row r="129" spans="7:11" x14ac:dyDescent="0.3">
+    <row r="129" spans="7:11" x14ac:dyDescent="0.2">
       <c r="G129">
         <v>9932.5</v>
       </c>
@@ -26897,7 +26897,7 @@
         <v>5995</v>
       </c>
     </row>
-    <row r="130" spans="7:11" x14ac:dyDescent="0.3">
+    <row r="130" spans="7:11" x14ac:dyDescent="0.2">
       <c r="G130">
         <v>9437</v>
       </c>
@@ -26914,7 +26914,7 @@
         <v>5985</v>
       </c>
     </row>
-    <row r="131" spans="7:11" x14ac:dyDescent="0.3">
+    <row r="131" spans="7:11" x14ac:dyDescent="0.2">
       <c r="G131">
         <v>9409</v>
       </c>
@@ -26931,7 +26931,7 @@
         <v>6020</v>
       </c>
     </row>
-    <row r="132" spans="7:11" x14ac:dyDescent="0.3">
+    <row r="132" spans="7:11" x14ac:dyDescent="0.2">
       <c r="G132">
         <v>9792.5</v>
       </c>
@@ -26948,7 +26948,7 @@
         <v>6075</v>
       </c>
     </row>
-    <row r="133" spans="7:11" x14ac:dyDescent="0.3">
+    <row r="133" spans="7:11" x14ac:dyDescent="0.2">
       <c r="G133">
         <v>7727.5</v>
       </c>
@@ -26965,7 +26965,7 @@
         <v>6075</v>
       </c>
     </row>
-    <row r="134" spans="7:11" x14ac:dyDescent="0.3">
+    <row r="134" spans="7:11" x14ac:dyDescent="0.2">
       <c r="G134">
         <v>7507.5</v>
       </c>
@@ -26982,7 +26982,7 @@
         <v>6075</v>
       </c>
     </row>
-    <row r="135" spans="7:11" x14ac:dyDescent="0.3">
+    <row r="135" spans="7:11" x14ac:dyDescent="0.2">
       <c r="G135">
         <v>7403</v>
       </c>
@@ -26999,7 +26999,7 @@
         <v>6145</v>
       </c>
     </row>
-    <row r="136" spans="7:11" x14ac:dyDescent="0.3">
+    <row r="136" spans="7:11" x14ac:dyDescent="0.2">
       <c r="G136">
         <v>6778.5</v>
       </c>
@@ -27016,7 +27016,7 @@
         <v>6145</v>
       </c>
     </row>
-    <row r="137" spans="7:11" x14ac:dyDescent="0.3">
+    <row r="137" spans="7:11" x14ac:dyDescent="0.2">
       <c r="G137">
         <v>7851.5</v>
       </c>
@@ -27033,7 +27033,7 @@
         <v>6175</v>
       </c>
     </row>
-    <row r="138" spans="7:11" x14ac:dyDescent="0.3">
+    <row r="138" spans="7:11" x14ac:dyDescent="0.2">
       <c r="G138">
         <v>7338.5</v>
       </c>
@@ -27050,7 +27050,7 @@
         <v>6175</v>
       </c>
     </row>
-    <row r="139" spans="7:11" x14ac:dyDescent="0.3">
+    <row r="139" spans="7:11" x14ac:dyDescent="0.2">
       <c r="G139">
         <v>8016.5</v>
       </c>
@@ -27067,7 +27067,7 @@
         <v>6175</v>
       </c>
     </row>
-    <row r="140" spans="7:11" x14ac:dyDescent="0.3">
+    <row r="140" spans="7:11" x14ac:dyDescent="0.2">
       <c r="G140">
         <v>9215.5</v>
       </c>
@@ -27084,7 +27084,7 @@
         <v>6195</v>
       </c>
     </row>
-    <row r="141" spans="7:11" x14ac:dyDescent="0.3">
+    <row r="141" spans="7:11" x14ac:dyDescent="0.2">
       <c r="G141">
         <v>9215</v>
       </c>
@@ -27101,7 +27101,7 @@
         <v>6195</v>
       </c>
     </row>
-    <row r="142" spans="7:11" x14ac:dyDescent="0.3">
+    <row r="142" spans="7:11" x14ac:dyDescent="0.2">
       <c r="G142">
         <v>7323.5</v>
       </c>
@@ -27118,7 +27118,7 @@
         <v>6200</v>
       </c>
     </row>
-    <row r="143" spans="7:11" x14ac:dyDescent="0.3">
+    <row r="143" spans="7:11" x14ac:dyDescent="0.2">
       <c r="G143">
         <v>9636.5</v>
       </c>
@@ -27135,7 +27135,7 @@
         <v>6115</v>
       </c>
     </row>
-    <row r="144" spans="7:11" x14ac:dyDescent="0.3">
+    <row r="144" spans="7:11" x14ac:dyDescent="0.2">
       <c r="G144">
         <v>8811.5</v>
       </c>
@@ -27152,7 +27152,7 @@
         <v>6115</v>
       </c>
     </row>
-    <row r="145" spans="7:11" x14ac:dyDescent="0.3">
+    <row r="145" spans="7:11" x14ac:dyDescent="0.2">
       <c r="G145">
         <v>7511.5</v>
       </c>
@@ -27169,7 +27169,7 @@
         <v>6195</v>
       </c>
     </row>
-    <row r="146" spans="7:11" x14ac:dyDescent="0.3">
+    <row r="146" spans="7:11" x14ac:dyDescent="0.2">
       <c r="G146">
         <v>6983.5</v>
       </c>
@@ -27186,7 +27186,7 @@
         <v>6210</v>
       </c>
     </row>
-    <row r="147" spans="7:11" x14ac:dyDescent="0.3">
+    <row r="147" spans="7:11" x14ac:dyDescent="0.2">
       <c r="G147">
         <v>10511</v>
       </c>
@@ -27203,7 +27203,7 @@
         <v>6210</v>
       </c>
     </row>
-    <row r="148" spans="7:11" x14ac:dyDescent="0.3">
+    <row r="148" spans="7:11" x14ac:dyDescent="0.2">
       <c r="G148">
         <v>11278</v>
       </c>
@@ -27220,7 +27220,7 @@
         <v>6210</v>
       </c>
     </row>
-    <row r="149" spans="7:11" x14ac:dyDescent="0.3">
+    <row r="149" spans="7:11" x14ac:dyDescent="0.2">
       <c r="G149">
         <v>7917.5</v>
       </c>
@@ -27237,7 +27237,7 @@
         <v>6210</v>
       </c>
     </row>
-    <row r="150" spans="7:11" x14ac:dyDescent="0.3">
+    <row r="150" spans="7:11" x14ac:dyDescent="0.2">
       <c r="G150">
         <v>11259.5</v>
       </c>
@@ -27262,9 +27262,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE6910FC-B2FB-4FC3-B18F-952D87906180}">
   <dimension ref="A1:B105"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -27272,7 +27272,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>0</v>
       </c>
@@ -27280,7 +27280,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3">
         <f>1+A2</f>
         <v>1</v>
@@ -27289,7 +27289,7 @@
         <v>4792.6400000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4">
         <f t="shared" ref="A4:A67" si="0">1+A3</f>
         <v>2</v>
@@ -27298,7 +27298,7 @@
         <v>5302.5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -27307,7 +27307,7 @@
         <v>5172.7700000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -27316,7 +27316,7 @@
         <v>5176.38</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -27325,7 +27325,7 @@
         <v>5276.81</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -27334,7 +27334,7 @@
         <v>5258.25</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -27343,7 +27343,7 @@
         <v>5371.61</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -27352,7 +27352,7 @@
         <v>2145.6999999999998</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -27361,7 +27361,7 @@
         <v>3014.7</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -27370,7 +27370,7 @@
         <v>5332.42</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -27379,7 +27379,7 @@
         <v>5136.9799999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -27388,7 +27388,7 @@
         <v>4942.18</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -27397,7 +27397,7 @@
         <v>4908.24</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -27406,7 +27406,7 @@
         <v>4853.96</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -27415,7 +27415,7 @@
         <v>4817.09</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -27424,7 +27424,7 @@
         <v>4744.05</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -27433,7 +27433,7 @@
         <v>4699.57</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -27442,7 +27442,7 @@
         <v>4804.79</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -27451,7 +27451,7 @@
         <v>4600.7299999999996</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -27460,7 +27460,7 @@
         <v>4797.68</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -27469,7 +27469,7 @@
         <v>5110.08</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -27478,7 +27478,7 @@
         <v>5078.75</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -27487,7 +27487,7 @@
         <v>5018.96</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -27496,7 +27496,7 @@
         <v>4011.86</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -27505,7 +27505,7 @@
         <v>4090.48</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -27514,7 +27514,7 @@
         <v>4913.46</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -27523,7 +27523,7 @@
         <v>4240.0200000000004</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -27532,7 +27532,7 @@
         <v>6509.79</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -27541,7 +27541,7 @@
         <v>7859.62</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -27550,7 +27550,7 @@
         <v>6363.76</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -27559,7 +27559,7 @@
         <v>7003.48</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -27568,7 +27568,7 @@
         <v>6958.76</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -27577,7 +27577,7 @@
         <v>6733.07</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -27586,7 +27586,7 @@
         <v>6469.06</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -27595,7 +27595,7 @@
         <v>6330.34</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -27604,7 +27604,7 @@
         <v>6039.73</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -27613,7 +27613,7 @@
         <v>6086.94</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -27622,7 +27622,7 @@
         <v>6109.5</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -27631,7 +27631,7 @@
         <v>6257.65</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -27640,7 +27640,7 @@
         <v>6082.85</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -27649,7 +27649,7 @@
         <v>5741.47</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -27658,7 +27658,7 @@
         <v>5662.94</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45">
         <f t="shared" si="0"/>
         <v>43</v>
@@ -27667,7 +27667,7 @@
         <v>5767.05</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46">
         <f t="shared" si="0"/>
         <v>44</v>
@@ -27676,7 +27676,7 @@
         <v>4777.08</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -27685,7 +27685,7 @@
         <v>5908.48</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -27694,7 +27694,7 @@
         <v>5807.5</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -27703,7 +27703,7 @@
         <v>5975.05</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50">
         <f t="shared" si="0"/>
         <v>48</v>
@@ -27712,7 +27712,7 @@
         <v>6344.21</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51">
         <f t="shared" si="0"/>
         <v>49</v>
@@ -27721,7 +27721,7 @@
         <v>5874.56</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52">
         <f t="shared" si="0"/>
         <v>50</v>
@@ -27730,7 +27730,7 @@
         <v>5909.35</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53">
         <f t="shared" si="0"/>
         <v>51</v>
@@ -27739,7 +27739,7 @@
         <v>5773.7</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A54">
         <f t="shared" si="0"/>
         <v>52</v>
@@ -27748,7 +27748,7 @@
         <v>5636.26</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A55">
         <f t="shared" si="0"/>
         <v>53</v>
@@ -27757,7 +27757,7 @@
         <v>5596.33</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A56">
         <f t="shared" si="0"/>
         <v>54</v>
@@ -27766,7 +27766,7 @@
         <v>5469.31</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A57">
         <f t="shared" si="0"/>
         <v>55</v>
@@ -27775,7 +27775,7 @@
         <v>5511.6</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A58">
         <f t="shared" si="0"/>
         <v>56</v>
@@ -27784,7 +27784,7 @@
         <v>5692.81</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A59">
         <f t="shared" si="0"/>
         <v>57</v>
@@ -27793,7 +27793,7 @@
         <v>6051.92</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A60">
         <f t="shared" si="0"/>
         <v>58</v>
@@ -27802,7 +27802,7 @@
         <v>6041.71</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A61">
         <f t="shared" si="0"/>
         <v>59</v>
@@ -27811,7 +27811,7 @@
         <v>6172.7</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A62">
         <f t="shared" si="0"/>
         <v>60</v>
@@ -27820,7 +27820,7 @@
         <v>3720.53</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A63">
         <f t="shared" si="0"/>
         <v>61</v>
@@ -27829,7 +27829,7 @@
         <v>2334.4899999999998</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A64">
         <f t="shared" si="0"/>
         <v>62</v>
@@ -27838,7 +27838,7 @@
         <v>5925.71</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A65">
         <f t="shared" si="0"/>
         <v>63</v>
@@ -27847,7 +27847,7 @@
         <v>6911.53</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A66">
         <f t="shared" si="0"/>
         <v>64</v>
@@ -27856,7 +27856,7 @@
         <v>7087.86</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A67">
         <f t="shared" si="0"/>
         <v>65</v>
@@ -27865,7 +27865,7 @@
         <v>7285.18</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A68">
         <f t="shared" ref="A68:A105" si="1">1+A67</f>
         <v>66</v>
@@ -27874,7 +27874,7 @@
         <v>7432.69</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A69">
         <f t="shared" si="1"/>
         <v>67</v>
@@ -27883,7 +27883,7 @@
         <v>7402.42</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A70">
         <f t="shared" si="1"/>
         <v>68</v>
@@ -27892,7 +27892,7 @@
         <v>7213.8</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A71">
         <f t="shared" si="1"/>
         <v>69</v>
@@ -27901,7 +27901,7 @@
         <v>7045.13</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A72">
         <f t="shared" si="1"/>
         <v>70</v>
@@ -27910,7 +27910,7 @@
         <v>6491.6</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A73">
         <f t="shared" si="1"/>
         <v>71</v>
@@ -27919,7 +27919,7 @@
         <v>6688.19</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A74">
         <f t="shared" si="1"/>
         <v>72</v>
@@ -27928,7 +27928,7 @@
         <v>6951.72</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A75">
         <f t="shared" si="1"/>
         <v>73</v>
@@ -27937,7 +27937,7 @@
         <v>6711.19</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A76">
         <f t="shared" si="1"/>
         <v>74</v>
@@ -27946,7 +27946,7 @@
         <v>6119.13</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A77">
         <f t="shared" si="1"/>
         <v>75</v>
@@ -27955,7 +27955,7 @@
         <v>5190.13</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A78">
         <f t="shared" si="1"/>
         <v>76</v>
@@ -27964,7 +27964,7 @@
         <v>4863.08</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A79">
         <f t="shared" si="1"/>
         <v>77</v>
@@ -27973,7 +27973,7 @@
         <v>6420.07</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A80">
         <f t="shared" si="1"/>
         <v>78</v>
@@ -27982,7 +27982,7 @@
         <v>6359.25</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A81">
         <f t="shared" si="1"/>
         <v>79</v>
@@ -27991,7 +27991,7 @@
         <v>5206.96</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A82">
         <f t="shared" si="1"/>
         <v>80</v>
@@ -28000,7 +28000,7 @@
         <v>6865.25</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A83">
         <f t="shared" si="1"/>
         <v>81</v>
@@ -28009,7 +28009,7 @@
         <v>6385.85</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A84">
         <f t="shared" si="1"/>
         <v>82</v>
@@ -28018,7 +28018,7 @@
         <v>6332.37</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A85">
         <f t="shared" si="1"/>
         <v>83</v>
@@ -28027,7 +28027,7 @@
         <v>5316.1</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A86">
         <f t="shared" si="1"/>
         <v>84</v>
@@ -28036,7 +28036,7 @@
         <v>6737.33</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A87">
         <f t="shared" si="1"/>
         <v>85</v>
@@ -28045,7 +28045,7 @@
         <v>6193.65</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A88">
         <f t="shared" si="1"/>
         <v>86</v>
@@ -28054,7 +28054,7 @@
         <v>6574.34</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A89">
         <f t="shared" si="1"/>
         <v>87</v>
@@ -28063,7 +28063,7 @@
         <v>6873.75</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A90">
         <f t="shared" si="1"/>
         <v>88</v>
@@ -28072,7 +28072,7 @@
         <v>6680.3</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A91">
         <f t="shared" si="1"/>
         <v>89</v>
@@ -28081,7 +28081,7 @@
         <v>6426.92</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A92">
         <f t="shared" si="1"/>
         <v>90</v>
@@ -28090,7 +28090,7 @@
         <v>6315.48</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A93">
         <f t="shared" si="1"/>
         <v>91</v>
@@ -28099,7 +28099,7 @@
         <v>5967.75</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A94">
         <f t="shared" si="1"/>
         <v>92</v>
@@ -28108,7 +28108,7 @@
         <v>6702.58</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A95">
         <f t="shared" si="1"/>
         <v>93</v>
@@ -28117,7 +28117,7 @@
         <v>6865.46</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A96">
         <f t="shared" si="1"/>
         <v>94</v>
@@ -28126,7 +28126,7 @@
         <v>7198.34</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A97">
         <f t="shared" si="1"/>
         <v>95</v>
@@ -28135,7 +28135,7 @@
         <v>7059.1</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A98">
         <f t="shared" si="1"/>
         <v>96</v>
@@ -28144,7 +28144,7 @@
         <v>5875.23</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A99">
         <f t="shared" si="1"/>
         <v>97</v>
@@ -28153,7 +28153,7 @@
         <v>6765.19</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A100">
         <f t="shared" si="1"/>
         <v>98</v>
@@ -28162,7 +28162,7 @@
         <v>6546.78</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A101">
         <f t="shared" si="1"/>
         <v>99</v>
@@ -28171,7 +28171,7 @@
         <v>6681.54</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A102">
         <f t="shared" si="1"/>
         <v>100</v>
@@ -28180,7 +28180,7 @@
         <v>6130.36</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A103">
         <f t="shared" si="1"/>
         <v>101</v>
@@ -28189,7 +28189,7 @@
         <v>6383.16</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A104">
         <f t="shared" si="1"/>
         <v>102</v>
@@ -28198,7 +28198,7 @@
         <v>6225.59</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A105">
         <f t="shared" si="1"/>
         <v>103</v>
@@ -28215,7 +28215,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40E2DEA9-EB38-4D51-97AD-82AF0A22C943}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/data/M3/M3selected.xlsx
+++ b/data/M3/M3selected.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10409"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lisavecchi/Desktop/segmentation/data/M3/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\segmentation\data\M3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B36D55E-EBF8-5741-A12B-85D45FDD1E0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6128479-58AC-48ED-8765-EB2BC006B301}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="3" xr2:uid="{688A4006-9200-421D-B73F-75AE198D8BAB}"/>
+    <workbookView xWindow="2268" yWindow="2268" windowWidth="17280" windowHeight="9960" activeTab="3" xr2:uid="{688A4006-9200-421D-B73F-75AE198D8BAB}"/>
   </bookViews>
   <sheets>
     <sheet name="M3 series" sheetId="1" r:id="rId1"/>
@@ -45,6 +45,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -138,7 +141,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normale" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -156,7 +159,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="it-IT"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -193,7 +196,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="it-IT"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -729,7 +732,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="it-IT"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1238255456"/>
@@ -788,7 +791,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="it-IT"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1238256416"/>
@@ -836,7 +839,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="it-IT"/>
+      <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -850,7 +853,7 @@
 <file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="it-IT"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -887,7 +890,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="it-IT"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -1304,7 +1307,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="it-IT"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1351667936"/>
@@ -1363,7 +1366,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="it-IT"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1351666976"/>
@@ -1404,7 +1407,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="it-IT"/>
+      <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -1418,7 +1421,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="it-IT"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1455,7 +1458,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="it-IT"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -1992,7 +1995,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="it-IT"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1299140368"/>
@@ -2051,7 +2054,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="it-IT"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1299139408"/>
@@ -2092,7 +2095,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="it-IT"/>
+      <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -2106,7 +2109,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="it-IT"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2143,7 +2146,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="it-IT"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -2680,7 +2683,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="it-IT"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1299138928"/>
@@ -2739,7 +2742,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="it-IT"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1299132208"/>
@@ -2780,7 +2783,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="it-IT"/>
+      <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -2794,7 +2797,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="it-IT"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2831,7 +2834,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="it-IT"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -3368,7 +3371,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="it-IT"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1299138448"/>
@@ -3427,7 +3430,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="it-IT"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1299135568"/>
@@ -3468,7 +3471,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="it-IT"/>
+      <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -3482,7 +3485,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="it-IT"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3519,7 +3522,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="it-IT"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -4056,7 +4059,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="it-IT"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1299139888"/>
@@ -4115,7 +4118,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="it-IT"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1299142768"/>
@@ -4156,7 +4159,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="it-IT"/>
+      <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -4170,7 +4173,7 @@
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="it-IT"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4207,7 +4210,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="it-IT"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -4624,7 +4627,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="it-IT"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1351668896"/>
@@ -4683,7 +4686,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="it-IT"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1351678496"/>
@@ -4724,7 +4727,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="it-IT"/>
+      <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -4738,7 +4741,7 @@
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="it-IT"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4775,7 +4778,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="it-IT"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -5192,7 +5195,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="it-IT"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1351676576"/>
@@ -5251,7 +5254,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="it-IT"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1351674176"/>
@@ -5292,7 +5295,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="it-IT"/>
+      <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -5306,7 +5309,7 @@
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="it-IT"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -5343,7 +5346,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="it-IT"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -5760,7 +5763,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="it-IT"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1351676576"/>
@@ -5819,7 +5822,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="it-IT"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1351672256"/>
@@ -5860,7 +5863,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="it-IT"/>
+      <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -5874,7 +5877,7 @@
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="it-IT"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -5911,7 +5914,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="it-IT"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -6328,7 +6331,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="it-IT"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1351667936"/>
@@ -6387,7 +6390,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="it-IT"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1351666976"/>
@@ -6428,7 +6431,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="it-IT"/>
+      <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -19122,9 +19125,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78542E84-EF4D-44A4-8837-BCCF362D5BC7}">
   <dimension ref="A1:ET11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:150" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:150" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -19456,7 +19459,7 @@
         <v>4249.63</v>
       </c>
     </row>
-    <row r="2" spans="1:150" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:150" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -19788,7 +19791,7 @@
         <v>6222.02</v>
       </c>
     </row>
-    <row r="3" spans="1:150" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:150" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -20120,7 +20123,7 @@
         <v>4646.5</v>
       </c>
     </row>
-    <row r="4" spans="1:150" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:150" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -20452,7 +20455,7 @@
         <v>5425</v>
       </c>
     </row>
-    <row r="5" spans="1:150" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:150" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -20784,7 +20787,7 @@
         <v>5294.78</v>
       </c>
     </row>
-    <row r="7" spans="1:150" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:150" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -21236,7 +21239,7 @@
         <v>11259.5</v>
       </c>
     </row>
-    <row r="8" spans="1:150" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:150" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -21688,7 +21691,7 @@
         <v>7190</v>
       </c>
     </row>
-    <row r="9" spans="1:150" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:150" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -22140,7 +22143,7 @@
         <v>7425</v>
       </c>
     </row>
-    <row r="10" spans="1:150" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:150" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -22592,7 +22595,7 @@
         <v>6505</v>
       </c>
     </row>
-    <row r="11" spans="1:150" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:150" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -23052,9 +23055,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86E7BF23-D5B3-4B32-ABE1-8AA2AD8385AD}">
   <dimension ref="A1:K150"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -23086,7 +23089,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>104</v>
       </c>
@@ -23118,7 +23121,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>8</v>
       </c>
@@ -23150,7 +23153,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -23182,7 +23185,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>0</v>
       </c>
@@ -23214,7 +23217,7 @@
         <v>1981</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>0</v>
       </c>
@@ -23246,7 +23249,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>3060.42</v>
       </c>
@@ -23278,7 +23281,7 @@
         <v>4815</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>3021.19</v>
       </c>
@@ -23310,7 +23313,7 @@
         <v>4820</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>3301.13</v>
       </c>
@@ -23342,7 +23345,7 @@
         <v>4835</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>3287.03</v>
       </c>
@@ -23374,7 +23377,7 @@
         <v>5020</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>3080.71</v>
       </c>
@@ -23406,7 +23409,7 @@
         <v>5020</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>3160.68</v>
       </c>
@@ -23438,7 +23441,7 @@
         <v>5030</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>3077.17</v>
       </c>
@@ -23470,7 +23473,7 @@
         <v>5060</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>3023.04</v>
       </c>
@@ -23502,7 +23505,7 @@
         <v>5060</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2976.01</v>
       </c>
@@ -23534,7 +23537,7 @@
         <v>5090</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>3199.55</v>
       </c>
@@ -23566,7 +23569,7 @@
         <v>5095</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>3219.28</v>
       </c>
@@ -23598,7 +23601,7 @@
         <v>5095</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>3266.87</v>
       </c>
@@ -23630,7 +23633,7 @@
         <v>5065</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>3228.6</v>
       </c>
@@ -23662,7 +23665,7 @@
         <v>5055</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>3108.45</v>
       </c>
@@ -23694,7 +23697,7 @@
         <v>5045</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>3052.15</v>
       </c>
@@ -23726,7 +23729,7 @@
         <v>5045</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>3081.1</v>
       </c>
@@ -23758,7 +23761,7 @@
         <v>5100</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>3072.48</v>
       </c>
@@ -23790,7 +23793,7 @@
         <v>5100</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>2989.99</v>
       </c>
@@ -23822,7 +23825,7 @@
         <v>5095</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>2983.53</v>
       </c>
@@ -23854,7 +23857,7 @@
         <v>5160</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>2978.99</v>
       </c>
@@ -23886,7 +23889,7 @@
         <v>5210</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>3075.09</v>
       </c>
@@ -23918,7 +23921,7 @@
         <v>5250</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>3259.02</v>
       </c>
@@ -23950,7 +23953,7 @@
         <v>5250</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>3252.64</v>
       </c>
@@ -23982,7 +23985,7 @@
         <v>5255</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>3197.5</v>
       </c>
@@ -24014,7 +24017,7 @@
         <v>5135</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>3095.91</v>
       </c>
@@ -24046,7 +24049,7 @@
         <v>5220</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>3213.78</v>
       </c>
@@ -24078,7 +24081,7 @@
         <v>5245</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>3174.21</v>
       </c>
@@ -24110,7 +24113,7 @@
         <v>5245</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>3196.42</v>
       </c>
@@ -24142,7 +24145,7 @@
         <v>5365</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>3752.91</v>
       </c>
@@ -24174,7 +24177,7 @@
         <v>5365</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>4238.37</v>
       </c>
@@ -24206,7 +24209,7 @@
         <v>5365</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>4140.09</v>
       </c>
@@ -24238,7 +24241,7 @@
         <v>5210</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>3959.7</v>
       </c>
@@ -24270,7 +24273,7 @@
         <v>5210</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>3892.21</v>
       </c>
@@ -24302,7 +24305,7 @@
         <v>5190</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>3892.16</v>
       </c>
@@ -24334,7 +24337,7 @@
         <v>5180</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>3757.58</v>
       </c>
@@ -24366,7 +24369,7 @@
         <v>5180</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>3738.49</v>
       </c>
@@ -24398,7 +24401,7 @@
         <v>5245</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>3626.78</v>
       </c>
@@ -24430,7 +24433,7 @@
         <v>5245</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>3658.79</v>
       </c>
@@ -24462,7 +24465,7 @@
         <v>5305</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>3723.11</v>
       </c>
@@ -24494,7 +24497,7 @@
         <v>5195</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>3710.43</v>
       </c>
@@ -24526,7 +24529,7 @@
         <v>5235</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>3640.67</v>
       </c>
@@ -24558,7 +24561,7 @@
         <v>5350</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>3676.83</v>
       </c>
@@ -24590,7 +24593,7 @@
         <v>5310</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>3642.97</v>
       </c>
@@ -24622,7 +24625,7 @@
         <v>5245</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>3676.8</v>
       </c>
@@ -24654,7 +24657,7 @@
         <v>5345</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>3635.68</v>
       </c>
@@ -24686,7 +24689,7 @@
         <v>5375</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>3687.71</v>
       </c>
@@ -24718,7 +24721,7 @@
         <v>5375</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>3649.13</v>
       </c>
@@ -24750,7 +24753,7 @@
         <v>5375</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>3857.15</v>
       </c>
@@ -24782,7 +24785,7 @@
         <v>5375</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>3930.03</v>
       </c>
@@ -24814,7 +24817,7 @@
         <v>5375</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>3737.96</v>
       </c>
@@ -24846,7 +24849,7 @@
         <v>5390</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>3774.24</v>
       </c>
@@ -24878,7 +24881,7 @@
         <v>5365</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>3767.55</v>
       </c>
@@ -24910,7 +24913,7 @@
         <v>5365</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>3699.6</v>
       </c>
@@ -24942,7 +24945,7 @@
         <v>5325</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>3620.3</v>
       </c>
@@ -24974,7 +24977,7 @@
         <v>5160</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>3641</v>
       </c>
@@ -25006,7 +25009,7 @@
         <v>5315</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>3656.02</v>
       </c>
@@ -25038,7 +25041,7 @@
         <v>5310</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>3710.94</v>
       </c>
@@ -25070,7 +25073,7 @@
         <v>5335</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>3913.79</v>
       </c>
@@ -25102,7 +25105,7 @@
         <v>5335</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>3829.84</v>
       </c>
@@ -25134,7 +25137,7 @@
         <v>5340</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>3856.37</v>
       </c>
@@ -25166,7 +25169,7 @@
         <v>5340</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>3712.15</v>
       </c>
@@ -25198,7 +25201,7 @@
         <v>5335</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>3829.26</v>
       </c>
@@ -25230,7 +25233,7 @@
         <v>5115</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>4048.86</v>
       </c>
@@ -25262,7 +25265,7 @@
         <v>5335</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>4420.1400000000003</v>
       </c>
@@ -25294,7 +25297,7 @@
         <v>5255</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>4603.3</v>
       </c>
@@ -25326,7 +25329,7 @@
         <v>5350</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>4738.4399999999996</v>
       </c>
@@ -25358,7 +25361,7 @@
         <v>4750</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>4762.83</v>
       </c>
@@ -25390,7 +25393,7 @@
         <v>5225</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>4812.26</v>
       </c>
@@ -25422,7 +25425,7 @@
         <v>5295</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>4816.1000000000004</v>
       </c>
@@ -25454,7 +25457,7 @@
         <v>5295</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>4680.41</v>
       </c>
@@ -25486,7 +25489,7 @@
         <v>5290</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>4521.21</v>
       </c>
@@ -25518,7 +25521,7 @@
         <v>5330</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>4586.8</v>
       </c>
@@ -25550,7 +25553,7 @@
         <v>5360</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>4585.28</v>
       </c>
@@ -25582,7 +25585,7 @@
         <v>5370</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>4556.63</v>
       </c>
@@ -25614,7 +25617,7 @@
         <v>5370</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>4292.6899999999996</v>
       </c>
@@ -25646,7 +25649,7 @@
         <v>5360</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>4261.42</v>
       </c>
@@ -25678,7 +25681,7 @@
         <v>5360</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>4235.59</v>
       </c>
@@ -25710,7 +25713,7 @@
         <v>5365</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>4258.32</v>
       </c>
@@ -25742,7 +25745,7 @@
         <v>5360</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>4321.97</v>
       </c>
@@ -25774,7 +25777,7 @@
         <v>5360</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>4245.4399999999996</v>
       </c>
@@ -25806,7 +25809,7 @@
         <v>5365</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>4274.12</v>
       </c>
@@ -25838,7 +25841,7 @@
         <v>5385</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>4149.42</v>
       </c>
@@ -25870,7 +25873,7 @@
         <v>5295</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>4155.7</v>
       </c>
@@ -25902,7 +25905,7 @@
         <v>5420</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>4117.26</v>
       </c>
@@ -25934,7 +25937,7 @@
         <v>5470</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>4204.07</v>
       </c>
@@ -25966,7 +25969,7 @@
         <v>5475</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>4041.04</v>
       </c>
@@ -25998,7 +26001,7 @@
         <v>5500</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>4157.26</v>
       </c>
@@ -26030,7 +26033,7 @@
         <v>5500</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>4141.84</v>
       </c>
@@ -26062,7 +26065,7 @@
         <v>5490</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>4183.8999999999996</v>
       </c>
@@ -26094,7 +26097,7 @@
         <v>5495</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>4215.3900000000003</v>
       </c>
@@ -26126,7 +26129,7 @@
         <v>5515</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>4138.8900000000003</v>
       </c>
@@ -26158,7 +26161,7 @@
         <v>5465</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>4031.36</v>
       </c>
@@ -26190,7 +26193,7 @@
         <v>5455</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>4339.38</v>
       </c>
@@ -26222,7 +26225,7 @@
         <v>5500</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>4509.34</v>
       </c>
@@ -26254,7 +26257,7 @@
         <v>5460</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>4547.25</v>
       </c>
@@ -26286,7 +26289,7 @@
         <v>5545</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>4542.51</v>
       </c>
@@ -26318,7 +26321,7 @@
         <v>5625</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>4381.08</v>
       </c>
@@ -26350,7 +26353,7 @@
         <v>5715</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>4405.63</v>
       </c>
@@ -26382,7 +26385,7 @@
         <v>5715</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>4377.0200000000004</v>
       </c>
@@ -26414,7 +26417,7 @@
         <v>5715</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>4371.18</v>
       </c>
@@ -26446,7 +26449,7 @@
         <v>5710</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>4255.07</v>
       </c>
@@ -26478,7 +26481,7 @@
         <v>5715</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>4285.4399999999996</v>
       </c>
@@ -26510,7 +26513,7 @@
         <v>5715</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>4260.68</v>
       </c>
@@ -26542,7 +26545,7 @@
         <v>5670</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>4249.63</v>
       </c>
@@ -26574,7 +26577,7 @@
         <v>5660</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
       <c r="G111">
         <v>4042.5</v>
       </c>
@@ -26591,7 +26594,7 @@
         <v>5695</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
       <c r="G112">
         <v>6155</v>
       </c>
@@ -26608,7 +26611,7 @@
         <v>5695</v>
       </c>
     </row>
-    <row r="113" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="113" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G113">
         <v>6226</v>
       </c>
@@ -26625,7 +26628,7 @@
         <v>5545</v>
       </c>
     </row>
-    <row r="114" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="114" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G114">
         <v>3912</v>
       </c>
@@ -26642,7 +26645,7 @@
         <v>5535</v>
       </c>
     </row>
-    <row r="115" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="115" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G115">
         <v>6016</v>
       </c>
@@ -26659,7 +26662,7 @@
         <v>5535</v>
       </c>
     </row>
-    <row r="116" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="116" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G116">
         <v>5424.5</v>
       </c>
@@ -26676,7 +26679,7 @@
         <v>5535</v>
       </c>
     </row>
-    <row r="117" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="117" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G117">
         <v>6525</v>
       </c>
@@ -26693,7 +26696,7 @@
         <v>5670</v>
       </c>
     </row>
-    <row r="118" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="118" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G118">
         <v>6826</v>
       </c>
@@ -26710,7 +26713,7 @@
         <v>5680</v>
       </c>
     </row>
-    <row r="119" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="119" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G119">
         <v>7280</v>
       </c>
@@ -26727,7 +26730,7 @@
         <v>5780</v>
       </c>
     </row>
-    <row r="120" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="120" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G120">
         <v>6972.5</v>
       </c>
@@ -26744,7 +26747,7 @@
         <v>5845</v>
       </c>
     </row>
-    <row r="121" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="121" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G121">
         <v>5951</v>
       </c>
@@ -26761,7 +26764,7 @@
         <v>5840</v>
       </c>
     </row>
-    <row r="122" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="122" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G122">
         <v>8384.5</v>
       </c>
@@ -26778,7 +26781,7 @@
         <v>5840</v>
       </c>
     </row>
-    <row r="123" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="123" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G123">
         <v>5751</v>
       </c>
@@ -26795,7 +26798,7 @@
         <v>5840</v>
       </c>
     </row>
-    <row r="124" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="124" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G124">
         <v>6521.5</v>
       </c>
@@ -26812,7 +26815,7 @@
         <v>5845</v>
       </c>
     </row>
-    <row r="125" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="125" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G125">
         <v>7001.5</v>
       </c>
@@ -26829,7 +26832,7 @@
         <v>5845</v>
       </c>
     </row>
-    <row r="126" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="126" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G126">
         <v>7790.5</v>
       </c>
@@ -26846,7 +26849,7 @@
         <v>5845</v>
       </c>
     </row>
-    <row r="127" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="127" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G127">
         <v>6086</v>
       </c>
@@ -26863,7 +26866,7 @@
         <v>5855</v>
       </c>
     </row>
-    <row r="128" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="128" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G128">
         <v>7812.5</v>
       </c>
@@ -26880,7 +26883,7 @@
         <v>5995</v>
       </c>
     </row>
-    <row r="129" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="129" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G129">
         <v>9932.5</v>
       </c>
@@ -26897,7 +26900,7 @@
         <v>5995</v>
       </c>
     </row>
-    <row r="130" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="130" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G130">
         <v>9437</v>
       </c>
@@ -26914,7 +26917,7 @@
         <v>5985</v>
       </c>
     </row>
-    <row r="131" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="131" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G131">
         <v>9409</v>
       </c>
@@ -26931,7 +26934,7 @@
         <v>6020</v>
       </c>
     </row>
-    <row r="132" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="132" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G132">
         <v>9792.5</v>
       </c>
@@ -26948,7 +26951,7 @@
         <v>6075</v>
       </c>
     </row>
-    <row r="133" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="133" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G133">
         <v>7727.5</v>
       </c>
@@ -26965,7 +26968,7 @@
         <v>6075</v>
       </c>
     </row>
-    <row r="134" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="134" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G134">
         <v>7507.5</v>
       </c>
@@ -26982,7 +26985,7 @@
         <v>6075</v>
       </c>
     </row>
-    <row r="135" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="135" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G135">
         <v>7403</v>
       </c>
@@ -26999,7 +27002,7 @@
         <v>6145</v>
       </c>
     </row>
-    <row r="136" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="136" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G136">
         <v>6778.5</v>
       </c>
@@ -27016,7 +27019,7 @@
         <v>6145</v>
       </c>
     </row>
-    <row r="137" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="137" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G137">
         <v>7851.5</v>
       </c>
@@ -27033,7 +27036,7 @@
         <v>6175</v>
       </c>
     </row>
-    <row r="138" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="138" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G138">
         <v>7338.5</v>
       </c>
@@ -27050,7 +27053,7 @@
         <v>6175</v>
       </c>
     </row>
-    <row r="139" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="139" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G139">
         <v>8016.5</v>
       </c>
@@ -27067,7 +27070,7 @@
         <v>6175</v>
       </c>
     </row>
-    <row r="140" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="140" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G140">
         <v>9215.5</v>
       </c>
@@ -27084,7 +27087,7 @@
         <v>6195</v>
       </c>
     </row>
-    <row r="141" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="141" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G141">
         <v>9215</v>
       </c>
@@ -27101,7 +27104,7 @@
         <v>6195</v>
       </c>
     </row>
-    <row r="142" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="142" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G142">
         <v>7323.5</v>
       </c>
@@ -27118,7 +27121,7 @@
         <v>6200</v>
       </c>
     </row>
-    <row r="143" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="143" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G143">
         <v>9636.5</v>
       </c>
@@ -27135,7 +27138,7 @@
         <v>6115</v>
       </c>
     </row>
-    <row r="144" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="144" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G144">
         <v>8811.5</v>
       </c>
@@ -27152,7 +27155,7 @@
         <v>6115</v>
       </c>
     </row>
-    <row r="145" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="145" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G145">
         <v>7511.5</v>
       </c>
@@ -27169,7 +27172,7 @@
         <v>6195</v>
       </c>
     </row>
-    <row r="146" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="146" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G146">
         <v>6983.5</v>
       </c>
@@ -27186,7 +27189,7 @@
         <v>6210</v>
       </c>
     </row>
-    <row r="147" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="147" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G147">
         <v>10511</v>
       </c>
@@ -27203,7 +27206,7 @@
         <v>6210</v>
       </c>
     </row>
-    <row r="148" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="148" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G148">
         <v>11278</v>
       </c>
@@ -27220,7 +27223,7 @@
         <v>6210</v>
       </c>
     </row>
-    <row r="149" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="149" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G149">
         <v>7917.5</v>
       </c>
@@ -27237,7 +27240,7 @@
         <v>6210</v>
       </c>
     </row>
-    <row r="150" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="150" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G150">
         <v>11259.5</v>
       </c>
@@ -27262,9 +27265,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE6910FC-B2FB-4FC3-B18F-952D87906180}">
   <dimension ref="A1:B105"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -27272,7 +27275,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -27280,7 +27283,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <f>1+A2</f>
         <v>1</v>
@@ -27289,7 +27292,7 @@
         <v>4792.6400000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <f t="shared" ref="A4:A67" si="0">1+A3</f>
         <v>2</v>
@@ -27298,7 +27301,7 @@
         <v>5302.5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -27307,7 +27310,7 @@
         <v>5172.7700000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -27316,7 +27319,7 @@
         <v>5176.38</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -27325,7 +27328,7 @@
         <v>5276.81</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -27334,7 +27337,7 @@
         <v>5258.25</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -27343,7 +27346,7 @@
         <v>5371.61</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -27352,7 +27355,7 @@
         <v>2145.6999999999998</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -27361,7 +27364,7 @@
         <v>3014.7</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -27370,7 +27373,7 @@
         <v>5332.42</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -27379,7 +27382,7 @@
         <v>5136.9799999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -27388,7 +27391,7 @@
         <v>4942.18</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -27397,7 +27400,7 @@
         <v>4908.24</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -27406,7 +27409,7 @@
         <v>4853.96</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -27415,7 +27418,7 @@
         <v>4817.09</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -27424,7 +27427,7 @@
         <v>4744.05</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -27433,7 +27436,7 @@
         <v>4699.57</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -27442,7 +27445,7 @@
         <v>4804.79</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -27451,7 +27454,7 @@
         <v>4600.7299999999996</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -27460,7 +27463,7 @@
         <v>4797.68</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -27469,7 +27472,7 @@
         <v>5110.08</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -27478,7 +27481,7 @@
         <v>5078.75</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -27487,7 +27490,7 @@
         <v>5018.96</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -27496,7 +27499,7 @@
         <v>4011.86</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -27505,7 +27508,7 @@
         <v>4090.48</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -27514,7 +27517,7 @@
         <v>4913.46</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -27523,7 +27526,7 @@
         <v>4240.0200000000004</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -27532,7 +27535,7 @@
         <v>6509.79</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -27541,7 +27544,7 @@
         <v>7859.62</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -27550,7 +27553,7 @@
         <v>6363.76</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -27559,7 +27562,7 @@
         <v>7003.48</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -27568,7 +27571,7 @@
         <v>6958.76</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -27577,7 +27580,7 @@
         <v>6733.07</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -27586,7 +27589,7 @@
         <v>6469.06</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -27595,7 +27598,7 @@
         <v>6330.34</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -27604,7 +27607,7 @@
         <v>6039.73</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -27613,7 +27616,7 @@
         <v>6086.94</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -27622,7 +27625,7 @@
         <v>6109.5</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -27631,7 +27634,7 @@
         <v>6257.65</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -27640,7 +27643,7 @@
         <v>6082.85</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -27649,7 +27652,7 @@
         <v>5741.47</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -27658,7 +27661,7 @@
         <v>5662.94</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45">
         <f t="shared" si="0"/>
         <v>43</v>
@@ -27667,7 +27670,7 @@
         <v>5767.05</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46">
         <f t="shared" si="0"/>
         <v>44</v>
@@ -27676,7 +27679,7 @@
         <v>4777.08</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -27685,7 +27688,7 @@
         <v>5908.48</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -27694,7 +27697,7 @@
         <v>5807.5</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -27703,7 +27706,7 @@
         <v>5975.05</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50">
         <f t="shared" si="0"/>
         <v>48</v>
@@ -27712,7 +27715,7 @@
         <v>6344.21</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51">
         <f t="shared" si="0"/>
         <v>49</v>
@@ -27721,7 +27724,7 @@
         <v>5874.56</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52">
         <f t="shared" si="0"/>
         <v>50</v>
@@ -27730,7 +27733,7 @@
         <v>5909.35</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53">
         <f t="shared" si="0"/>
         <v>51</v>
@@ -27739,7 +27742,7 @@
         <v>5773.7</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54">
         <f t="shared" si="0"/>
         <v>52</v>
@@ -27748,7 +27751,7 @@
         <v>5636.26</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55">
         <f t="shared" si="0"/>
         <v>53</v>
@@ -27757,7 +27760,7 @@
         <v>5596.33</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56">
         <f t="shared" si="0"/>
         <v>54</v>
@@ -27766,7 +27769,7 @@
         <v>5469.31</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57">
         <f t="shared" si="0"/>
         <v>55</v>
@@ -27775,7 +27778,7 @@
         <v>5511.6</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58">
         <f t="shared" si="0"/>
         <v>56</v>
@@ -27784,7 +27787,7 @@
         <v>5692.81</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59">
         <f t="shared" si="0"/>
         <v>57</v>
@@ -27793,7 +27796,7 @@
         <v>6051.92</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60">
         <f t="shared" si="0"/>
         <v>58</v>
@@ -27802,7 +27805,7 @@
         <v>6041.71</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61">
         <f t="shared" si="0"/>
         <v>59</v>
@@ -27811,7 +27814,7 @@
         <v>6172.7</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62">
         <f t="shared" si="0"/>
         <v>60</v>
@@ -27820,7 +27823,7 @@
         <v>3720.53</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63">
         <f t="shared" si="0"/>
         <v>61</v>
@@ -27829,7 +27832,7 @@
         <v>2334.4899999999998</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64">
         <f t="shared" si="0"/>
         <v>62</v>
@@ -27838,7 +27841,7 @@
         <v>5925.71</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65">
         <f t="shared" si="0"/>
         <v>63</v>
@@ -27847,7 +27850,7 @@
         <v>6911.53</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66">
         <f t="shared" si="0"/>
         <v>64</v>
@@ -27856,7 +27859,7 @@
         <v>7087.86</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67">
         <f t="shared" si="0"/>
         <v>65</v>
@@ -27865,7 +27868,7 @@
         <v>7285.18</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68">
         <f t="shared" ref="A68:A105" si="1">1+A67</f>
         <v>66</v>
@@ -27874,7 +27877,7 @@
         <v>7432.69</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69">
         <f t="shared" si="1"/>
         <v>67</v>
@@ -27883,7 +27886,7 @@
         <v>7402.42</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70">
         <f t="shared" si="1"/>
         <v>68</v>
@@ -27892,7 +27895,7 @@
         <v>7213.8</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71">
         <f t="shared" si="1"/>
         <v>69</v>
@@ -27901,7 +27904,7 @@
         <v>7045.13</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72">
         <f t="shared" si="1"/>
         <v>70</v>
@@ -27910,7 +27913,7 @@
         <v>6491.6</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73">
         <f t="shared" si="1"/>
         <v>71</v>
@@ -27919,7 +27922,7 @@
         <v>6688.19</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74">
         <f t="shared" si="1"/>
         <v>72</v>
@@ -27928,7 +27931,7 @@
         <v>6951.72</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75">
         <f t="shared" si="1"/>
         <v>73</v>
@@ -27937,7 +27940,7 @@
         <v>6711.19</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76">
         <f t="shared" si="1"/>
         <v>74</v>
@@ -27946,7 +27949,7 @@
         <v>6119.13</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77">
         <f t="shared" si="1"/>
         <v>75</v>
@@ -27955,7 +27958,7 @@
         <v>5190.13</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78">
         <f t="shared" si="1"/>
         <v>76</v>
@@ -27964,7 +27967,7 @@
         <v>4863.08</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79">
         <f t="shared" si="1"/>
         <v>77</v>
@@ -27973,7 +27976,7 @@
         <v>6420.07</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80">
         <f t="shared" si="1"/>
         <v>78</v>
@@ -27982,7 +27985,7 @@
         <v>6359.25</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81">
         <f t="shared" si="1"/>
         <v>79</v>
@@ -27991,7 +27994,7 @@
         <v>5206.96</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82">
         <f t="shared" si="1"/>
         <v>80</v>
@@ -28000,7 +28003,7 @@
         <v>6865.25</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83">
         <f t="shared" si="1"/>
         <v>81</v>
@@ -28009,7 +28012,7 @@
         <v>6385.85</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84">
         <f t="shared" si="1"/>
         <v>82</v>
@@ -28018,7 +28021,7 @@
         <v>6332.37</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85">
         <f t="shared" si="1"/>
         <v>83</v>
@@ -28027,7 +28030,7 @@
         <v>5316.1</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86">
         <f t="shared" si="1"/>
         <v>84</v>
@@ -28036,7 +28039,7 @@
         <v>6737.33</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87">
         <f t="shared" si="1"/>
         <v>85</v>
@@ -28045,7 +28048,7 @@
         <v>6193.65</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88">
         <f t="shared" si="1"/>
         <v>86</v>
@@ -28054,7 +28057,7 @@
         <v>6574.34</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89">
         <f t="shared" si="1"/>
         <v>87</v>
@@ -28063,7 +28066,7 @@
         <v>6873.75</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90">
         <f t="shared" si="1"/>
         <v>88</v>
@@ -28072,7 +28075,7 @@
         <v>6680.3</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91">
         <f t="shared" si="1"/>
         <v>89</v>
@@ -28081,7 +28084,7 @@
         <v>6426.92</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92">
         <f t="shared" si="1"/>
         <v>90</v>
@@ -28090,7 +28093,7 @@
         <v>6315.48</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93">
         <f t="shared" si="1"/>
         <v>91</v>
@@ -28099,7 +28102,7 @@
         <v>5967.75</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94">
         <f t="shared" si="1"/>
         <v>92</v>
@@ -28108,7 +28111,7 @@
         <v>6702.58</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95">
         <f t="shared" si="1"/>
         <v>93</v>
@@ -28117,7 +28120,7 @@
         <v>6865.46</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96">
         <f t="shared" si="1"/>
         <v>94</v>
@@ -28126,7 +28129,7 @@
         <v>7198.34</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97">
         <f t="shared" si="1"/>
         <v>95</v>
@@ -28135,7 +28138,7 @@
         <v>7059.1</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98">
         <f t="shared" si="1"/>
         <v>96</v>
@@ -28144,7 +28147,7 @@
         <v>5875.23</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99">
         <f t="shared" si="1"/>
         <v>97</v>
@@ -28153,7 +28156,7 @@
         <v>6765.19</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100">
         <f t="shared" si="1"/>
         <v>98</v>
@@ -28162,7 +28165,7 @@
         <v>6546.78</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101">
         <f t="shared" si="1"/>
         <v>99</v>
@@ -28171,7 +28174,7 @@
         <v>6681.54</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102">
         <f t="shared" si="1"/>
         <v>100</v>
@@ -28180,7 +28183,7 @@
         <v>6130.36</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103">
         <f t="shared" si="1"/>
         <v>101</v>
@@ -28189,7 +28192,7 @@
         <v>6383.16</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104">
         <f t="shared" si="1"/>
         <v>102</v>
@@ -28198,7 +28201,7 @@
         <v>6225.59</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105">
         <f t="shared" si="1"/>
         <v>103</v>
@@ -28215,7 +28218,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40E2DEA9-EB38-4D51-97AD-82AF0A22C943}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
